--- a/exports/trend_1d/MIDCPNIFTY_full_report.xlsx
+++ b/exports/trend_1d/MIDCPNIFTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q185"/>
+  <dimension ref="A1:U185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42039</v>
+        <v>42040</v>
       </c>
       <c r="H2" t="n">
-        <v>2855.21</v>
+        <v>2811.83</v>
       </c>
       <c r="I2" t="n">
         <v>2841.393846158403</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>1.85</v>
+        <v>0.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.61</v>
+        <v>1.52</v>
       </c>
       <c r="N2" t="n">
-        <v>0.61</v>
+        <v>1.52</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>2.01</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42045</v>
+        <v>42046</v>
       </c>
       <c r="H3" t="n">
-        <v>2745.45</v>
+        <v>2818.95</v>
       </c>
       <c r="I3" t="n">
         <v>2795.079985481925</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.36</v>
+        <v>-0.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.79</v>
+        <v>2.68</v>
       </c>
       <c r="N3" t="n">
-        <v>0.79</v>
+        <v>2.68</v>
       </c>
       <c r="O3" t="n">
         <v>-1.52</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>3.04</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42060</v>
+        <v>42061</v>
       </c>
       <c r="H4" t="n">
-        <v>2878.53</v>
+        <v>2835.02</v>
       </c>
       <c r="I4" t="n">
         <v>2837.486805483656</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>2.11</v>
+        <v>0.57</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="N4" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
         <v>2.68</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>2.51</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42063</v>
+        <v>42065</v>
       </c>
       <c r="H5" t="n">
-        <v>2900.12</v>
+        <v>2972.36</v>
       </c>
       <c r="I5" t="n">
         <v>2906.053221922174</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.3</v>
+        <v>-4.84</v>
       </c>
       <c r="L5" t="n">
-        <v>2.49</v>
+        <v>4.84</v>
       </c>
       <c r="M5" t="n">
         <v>2.49</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>3.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H6" t="n">
-        <v>2970.57</v>
+        <v>2898.77</v>
       </c>
       <c r="I6" t="n">
         <v>2906.045562096862</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.06</v>
+        <v>-2.48</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="M6" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="N6" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
         <v>2.49</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>3.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42094</v>
+        <v>42095</v>
       </c>
       <c r="H7" t="n">
-        <v>2847.32</v>
+        <v>2882.67</v>
       </c>
       <c r="I7" t="n">
         <v>2867.030080379484</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K7" t="n">
-        <v>1.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>1.06</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>2.5</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H8" t="n">
-        <v>2933.53</v>
+        <v>2888.34</v>
       </c>
       <c r="I8" t="n">
         <v>2930.248953117511</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>1.76</v>
+        <v>0.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="O8" t="n">
         <v>1.24</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>2.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42123</v>
+        <v>42124</v>
       </c>
       <c r="H9" t="n">
-        <v>2789.82</v>
+        <v>2804.29</v>
       </c>
       <c r="I9" t="n">
         <v>2791.622235884526</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>3.41</v>
+        <v>2.91</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>3.46</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H10" t="n">
-        <v>2843.51</v>
+        <v>2718.3</v>
       </c>
       <c r="I10" t="n">
         <v>2754.422221132546</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>-3.07</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
         <v>0.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>4.33</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42132</v>
+        <v>42135</v>
       </c>
       <c r="H11" t="n">
-        <v>2735.18</v>
+        <v>2792.55</v>
       </c>
       <c r="I11" t="n">
         <v>2786.397800882638</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.62</v>
+        <v>-2.73</v>
       </c>
       <c r="L11" t="n">
-        <v>0.62</v>
+        <v>2.73</v>
       </c>
       <c r="M11" t="n">
         <v>2.66</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.85</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42156</v>
+        <v>42157</v>
       </c>
       <c r="H12" t="n">
-        <v>2941.1</v>
+        <v>2859.84</v>
       </c>
       <c r="I12" t="n">
         <v>2870.606517926385</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>5.32</v>
+        <v>2.41</v>
       </c>
       <c r="L12" t="n">
         <v>2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="N12" t="n">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="O12" t="n">
         <v>2.1</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.07</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42172</v>
+        <v>42173</v>
       </c>
       <c r="H13" t="n">
-        <v>2764.81</v>
+        <v>2785.32</v>
       </c>
       <c r="I13" t="n">
         <v>2783.891050830068</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K13" t="n">
-        <v>3.32</v>
+        <v>2.61</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>2.7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H14" t="n">
-        <v>3114.71</v>
+        <v>3023.61</v>
       </c>
       <c r="I14" t="n">
         <v>3089.384004827458</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K14" t="n">
-        <v>11.83</v>
+        <v>8.56</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.92</v>
+        <v>2.92</v>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
         <v>0.74</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>2.77</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42230</v>
+        <v>42233</v>
       </c>
       <c r="H15" t="n">
-        <v>3078.05</v>
+        <v>3095.18</v>
       </c>
       <c r="I15" t="n">
         <v>3092.845370480783</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.8</v>
+        <v>-2.37</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
         <v>2.1</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>2.76</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H16" t="n">
-        <v>3058.35</v>
+        <v>3030.98</v>
       </c>
       <c r="I16" t="n">
         <v>3045.392514919509</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.19</v>
+        <v>-2.07</v>
       </c>
       <c r="L16" t="n">
-        <v>1.19</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
         <v>1.98</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>3.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42276</v>
+        <v>42277</v>
       </c>
       <c r="H17" t="n">
-        <v>2866.09</v>
+        <v>2906.39</v>
       </c>
       <c r="I17" t="n">
         <v>2877.391251296698</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" t="n">
-        <v>5.44</v>
+        <v>4.11</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42304</v>
+        <v>42305</v>
       </c>
       <c r="H18" t="n">
-        <v>2983.31</v>
+        <v>2961.67</v>
       </c>
       <c r="I18" t="n">
         <v>2963.482546120219</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K18" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>1.65</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42324</v>
+        <v>42325</v>
       </c>
       <c r="H19" t="n">
-        <v>2876.73</v>
+        <v>2905.41</v>
       </c>
       <c r="I19" t="n">
         <v>2899.004215662335</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>2.87</v>
+        <v>1.9</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>2.32</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42345</v>
+        <v>42346</v>
       </c>
       <c r="H20" t="n">
-        <v>2975.92</v>
+        <v>2941.89</v>
       </c>
       <c r="I20" t="n">
         <v>2968.837390624869</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>2.43</v>
+        <v>1.26</v>
       </c>
       <c r="L20" t="n">
         <v>0.9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>1.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42354</v>
+        <v>42355</v>
       </c>
       <c r="H21" t="n">
-        <v>2923.8</v>
+        <v>2969.72</v>
       </c>
       <c r="I21" t="n">
         <v>2950.457700848929</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M21" t="n">
         <v>1.58</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>2.57</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H22" t="n">
-        <v>3061.29</v>
+        <v>2958.11</v>
       </c>
       <c r="I22" t="n">
         <v>3023.725905748667</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>3.08</v>
+        <v>-0.39</v>
       </c>
       <c r="L22" t="n">
         <v>0.39</v>
       </c>
       <c r="M22" t="n">
-        <v>0.95</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="n">
-        <v>0.95</v>
+        <v>3.37</v>
       </c>
       <c r="O22" t="n">
         <v>1.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>3.02</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>42398</v>
+        <v>42401</v>
       </c>
       <c r="H23" t="n">
-        <v>2783.8</v>
+        <v>2797.24</v>
       </c>
       <c r="I23" t="n">
         <v>2788.730722151327</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>5.89</v>
+        <v>5.44</v>
       </c>
       <c r="L23" t="n">
         <v>1.06</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>3.49</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>42403</v>
+        <v>42404</v>
       </c>
       <c r="H24" t="n">
-        <v>2712.25</v>
+        <v>2689.69</v>
       </c>
       <c r="I24" t="n">
         <v>2699.724458629177</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.04</v>
+        <v>-3.84</v>
       </c>
       <c r="L24" t="n">
-        <v>3.04</v>
+        <v>3.84</v>
       </c>
       <c r="M24" t="n">
         <v>2.04</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>3.72</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H25" t="n">
-        <v>2603.21</v>
+        <v>2685.35</v>
       </c>
       <c r="I25" t="n">
         <v>2616.623339669312</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25" t="n">
-        <v>3.22</v>
+        <v>0.16</v>
       </c>
       <c r="L25" t="n">
         <v>2.61</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>4.9</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>42464</v>
+        <v>42465</v>
       </c>
       <c r="H26" t="n">
-        <v>2883.78</v>
+        <v>2810.83</v>
       </c>
       <c r="I26" t="n">
         <v>2814.758625619327</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>7.39</v>
+        <v>4.67</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.38</v>
+        <v>2.53</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>2.53</v>
       </c>
       <c r="O26" t="n">
         <v>3.16</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>3.1</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>42471</v>
+        <v>42472</v>
       </c>
       <c r="H27" t="n">
-        <v>2878.02</v>
+        <v>2911.35</v>
       </c>
       <c r="I27" t="n">
         <v>2897.834713248345</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.39</v>
+        <v>-3.58</v>
       </c>
       <c r="L27" t="n">
-        <v>2.39</v>
+        <v>3.58</v>
       </c>
       <c r="M27" t="n">
         <v>1.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>42488</v>
+        <v>42489</v>
       </c>
       <c r="H28" t="n">
-        <v>2976.96</v>
+        <v>2971.61</v>
       </c>
       <c r="I28" t="n">
         <v>2973.801359537139</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>2.68</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>42501</v>
+        <v>42502</v>
       </c>
       <c r="H29" t="n">
-        <v>2993.63</v>
+        <v>3019.54</v>
       </c>
       <c r="I29" t="n">
         <v>3011.217730786223</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.74</v>
+        <v>-1.61</v>
       </c>
       <c r="L29" t="n">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="M29" t="n">
         <v>1.31</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>2.29</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H30" t="n">
-        <v>2983.2</v>
+        <v>2955.22</v>
       </c>
       <c r="I30" t="n">
         <v>2981.696843058302</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.2</v>
+        <v>-2.13</v>
       </c>
       <c r="L30" t="n">
-        <v>1.2</v>
+        <v>2.13</v>
       </c>
       <c r="M30" t="n">
         <v>1.51</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>1.87</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>42515</v>
+        <v>42516</v>
       </c>
       <c r="H31" t="n">
-        <v>2991.79</v>
+        <v>3039.52</v>
       </c>
       <c r="I31" t="n">
         <v>2994.575345269449</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.24</v>
+        <v>-2.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.24</v>
+        <v>2.85</v>
       </c>
       <c r="M31" t="n">
         <v>1.74</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>2.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>42544</v>
+        <v>42545</v>
       </c>
       <c r="H32" t="n">
-        <v>3087.64</v>
+        <v>3038.06</v>
       </c>
       <c r="I32" t="n">
         <v>3045.11828463817</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K32" t="n">
-        <v>1.58</v>
+        <v>-0.05</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8</v>
+        <v>1.61</v>
       </c>
       <c r="N32" t="n">
-        <v>0.8</v>
+        <v>1.61</v>
       </c>
       <c r="O32" t="n">
         <v>1.6</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>1.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>42549</v>
+        <v>42550</v>
       </c>
       <c r="H33" t="n">
-        <v>3080.91</v>
+        <v>3126.25</v>
       </c>
       <c r="I33" t="n">
         <v>3098.148640498774</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.41</v>
+        <v>-2.9</v>
       </c>
       <c r="L33" t="n">
-        <v>1.41</v>
+        <v>2.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0.71</v>
+        <v>1.47</v>
       </c>
       <c r="N33" t="n">
-        <v>0.71</v>
+        <v>1.47</v>
       </c>
       <c r="O33" t="n">
         <v>-1.61</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>2.19</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>42569</v>
+        <v>42570</v>
       </c>
       <c r="H34" t="n">
-        <v>3195.64</v>
+        <v>3187.41</v>
       </c>
       <c r="I34" t="n">
         <v>3190.359880064766</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>2.14</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>42573</v>
+        <v>42576</v>
       </c>
       <c r="H35" t="n">
-        <v>3242.63</v>
+        <v>3289.52</v>
       </c>
       <c r="I35" t="n">
         <v>3255.630545420557</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.73</v>
+        <v>-3.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
         <v>1.53</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>2.77</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H36" t="n">
-        <v>3346.87</v>
+        <v>3277.97</v>
       </c>
       <c r="I36" t="n">
         <v>3286.899444132131</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>1.74</v>
+        <v>-0.35</v>
       </c>
       <c r="L36" t="n">
         <v>0.98</v>
       </c>
       <c r="M36" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
       <c r="N36" t="n">
-        <v>0.98</v>
+        <v>2.06</v>
       </c>
       <c r="O36" t="n">
         <v>1.45</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>3.2</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>42600</v>
+        <v>42601</v>
       </c>
       <c r="H37" t="n">
-        <v>3376.03</v>
+        <v>3412.97</v>
       </c>
       <c r="I37" t="n">
         <v>3382.726550252974</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.99</v>
+        <v>-4.12</v>
       </c>
       <c r="L37" t="n">
-        <v>2.99</v>
+        <v>4.12</v>
       </c>
       <c r="M37" t="n">
         <v>2.14</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>2.33</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>42622</v>
+        <v>42625</v>
       </c>
       <c r="H38" t="n">
-        <v>3585.61</v>
+        <v>3446.53</v>
       </c>
       <c r="I38" t="n">
         <v>3531.971025339823</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>5.06</v>
+        <v>0.98</v>
       </c>
       <c r="L38" t="n">
         <v>1.61</v>
       </c>
       <c r="M38" t="n">
-        <v>1.61</v>
+        <v>3.88</v>
       </c>
       <c r="N38" t="n">
-        <v>1.61</v>
+        <v>3.88</v>
       </c>
       <c r="O38" t="n">
         <v>1.09</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>3.34</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>42629</v>
+        <v>42632</v>
       </c>
       <c r="H39" t="n">
-        <v>3541.46</v>
+        <v>3585.96</v>
       </c>
       <c r="I39" t="n">
         <v>3561.703969474744</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.75</v>
+        <v>-4.05</v>
       </c>
       <c r="L39" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="M39" t="n">
         <v>2.59</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>3.07</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H40" t="n">
-        <v>3684.7</v>
+        <v>3532.43</v>
       </c>
       <c r="I40" t="n">
         <v>3578.793177568962</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>2.75</v>
+        <v>-1.49</v>
       </c>
       <c r="L40" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0.82</v>
+        <v>4.13</v>
       </c>
       <c r="N40" t="n">
-        <v>0.82</v>
+        <v>4.13</v>
       </c>
       <c r="O40" t="n">
         <v>1.26</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>3.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>42643</v>
+        <v>42646</v>
       </c>
       <c r="H41" t="n">
-        <v>3631.76</v>
+        <v>3733.77</v>
       </c>
       <c r="I41" t="n">
         <v>3673.427140187934</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.81</v>
+        <v>-5.7</v>
       </c>
       <c r="L41" t="n">
-        <v>2.81</v>
+        <v>5.7</v>
       </c>
       <c r="M41" t="n">
         <v>2.81</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.6</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>42675</v>
+        <v>42676</v>
       </c>
       <c r="H42" t="n">
-        <v>3743.16</v>
+        <v>3656.12</v>
       </c>
       <c r="I42" t="n">
         <v>3691.584742360476</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>0.25</v>
+        <v>-2.08</v>
       </c>
       <c r="L42" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="M42" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="N42" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="O42" t="n">
         <v>2.81</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>3.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>42703</v>
+        <v>42704</v>
       </c>
       <c r="H43" t="n">
-        <v>3336.6</v>
+        <v>3392.09</v>
       </c>
       <c r="I43" t="n">
         <v>3355.833744801756</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>8.74</v>
+        <v>7.22</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.35</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>42723</v>
+        <v>42724</v>
       </c>
       <c r="H44" t="n">
-        <v>3288.62</v>
+        <v>3223.99</v>
       </c>
       <c r="I44" t="n">
         <v>3266.678351518569</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.05</v>
+        <v>-4.96</v>
       </c>
       <c r="L44" t="n">
-        <v>3.56</v>
+        <v>4.96</v>
       </c>
       <c r="M44" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="N44" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="O44" t="n">
         <v>1.66</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>3.44</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>42732</v>
+        <v>42733</v>
       </c>
       <c r="H45" t="n">
-        <v>3155.92</v>
+        <v>3220.51</v>
       </c>
       <c r="I45" t="n">
         <v>3187.136097539876</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>2.11</v>
+        <v>0.11</v>
       </c>
       <c r="L45" t="n">
         <v>0.06</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>3.91</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H46" t="n">
-        <v>3586.85</v>
+        <v>3519.32</v>
       </c>
       <c r="I46" t="n">
         <v>3536.997137221072</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="n">
-        <v>11.38</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="N46" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O46" t="n">
         <v>2.05</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>2.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>42782</v>
+        <v>42783</v>
       </c>
       <c r="H47" t="n">
-        <v>3577.79</v>
+        <v>3607.87</v>
       </c>
       <c r="I47" t="n">
         <v>3602.486226965839</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.66</v>
+        <v>-2.52</v>
       </c>
       <c r="L47" t="n">
-        <v>1.66</v>
+        <v>2.52</v>
       </c>
       <c r="M47" t="n">
         <v>1.66</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>2.55</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H48" t="n">
-        <v>4160.66</v>
+        <v>4042.28</v>
       </c>
       <c r="I48" t="n">
         <v>4107.815940492213</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K48" t="n">
-        <v>15.32</v>
+        <v>12.04</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.74</v>
+        <v>2.85</v>
       </c>
       <c r="N48" t="n">
-        <v>1.74</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
         <v>0.84</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>2.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H49" t="n">
-        <v>3935.82</v>
+        <v>4003.47</v>
       </c>
       <c r="I49" t="n">
         <v>3955.690916068878</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>2.63</v>
+        <v>0.96</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>3.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>42908</v>
+        <v>42909</v>
       </c>
       <c r="H50" t="n">
-        <v>4078.43</v>
+        <v>4017.45</v>
       </c>
       <c r="I50" t="n">
         <v>4042.784723927718</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>1.87</v>
+        <v>0.35</v>
       </c>
       <c r="L50" t="n">
         <v>1.75</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>1.84</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>42916</v>
+        <v>42919</v>
       </c>
       <c r="H51" t="n">
-        <v>4011.34</v>
+        <v>4059.15</v>
       </c>
       <c r="I51" t="n">
         <v>4046.533830631024</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K51" t="n">
-        <v>0.15</v>
+        <v>-1.04</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="M51" t="n">
-        <v>0.58</v>
+        <v>1.19</v>
       </c>
       <c r="N51" t="n">
-        <v>0.58</v>
+        <v>1.19</v>
       </c>
       <c r="O51" t="n">
         <v>-1.5</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>1.98</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H52" t="n">
-        <v>4179.47</v>
+        <v>4176.42</v>
       </c>
       <c r="I52" t="n">
         <v>4178.215926761754</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K52" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="L52" t="n">
         <v>0.1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>1.51</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>42958</v>
+        <v>42961</v>
       </c>
       <c r="H53" t="n">
-        <v>3970.83</v>
+        <v>4091.36</v>
       </c>
       <c r="I53" t="n">
         <v>4078.326104864227</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K53" t="n">
-        <v>4.92</v>
+        <v>2.04</v>
       </c>
       <c r="L53" t="n">
         <v>0.98</v>
       </c>
       <c r="M53" t="n">
-        <v>0.98</v>
+        <v>3.04</v>
       </c>
       <c r="N53" t="n">
-        <v>0.98</v>
+        <v>3.04</v>
       </c>
       <c r="O53" t="n">
         <v>-0.07000000000000001</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>3.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H54" t="n">
-        <v>4327.62</v>
+        <v>4210.93</v>
       </c>
       <c r="I54" t="n">
         <v>4280.179877418442</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K54" t="n">
-        <v>5.77</v>
+        <v>2.92</v>
       </c>
       <c r="L54" t="n">
         <v>1.99</v>
       </c>
       <c r="M54" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="N54" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="O54" t="n">
         <v>3.04</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>2.77</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>43013</v>
+        <v>43014</v>
       </c>
       <c r="H55" t="n">
-        <v>4211.59</v>
+        <v>4263.18</v>
       </c>
       <c r="I55" t="n">
         <v>4236.087705434866</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.02</v>
+        <v>-1.24</v>
       </c>
       <c r="L55" t="n">
-        <v>0.02</v>
+        <v>1.24</v>
       </c>
       <c r="M55" t="n">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="N55" t="n">
-        <v>0.83</v>
+        <v>1.22</v>
       </c>
       <c r="O55" t="n">
         <v>-2.7</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>2.56</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>43045</v>
+        <v>43046</v>
       </c>
       <c r="H56" t="n">
-        <v>4468.17</v>
+        <v>4404.22</v>
       </c>
       <c r="I56" t="n">
         <v>4407.771797895129</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K56" t="n">
-        <v>4.81</v>
+        <v>3.31</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
       <c r="N56" t="n">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
       <c r="O56" t="n">
         <v>1.22</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>1.67</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>43055</v>
+        <v>43056</v>
       </c>
       <c r="H57" t="n">
-        <v>4444.21</v>
+        <v>4481.14</v>
       </c>
       <c r="I57" t="n">
         <v>4450.340043704946</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.91</v>
+        <v>-1.75</v>
       </c>
       <c r="L57" t="n">
-        <v>0.91</v>
+        <v>1.75</v>
       </c>
       <c r="M57" t="n">
         <v>1.36</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>1.75</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>43069</v>
+        <v>43070</v>
       </c>
       <c r="H58" t="n">
-        <v>4542.1</v>
+        <v>4501.3</v>
       </c>
       <c r="I58" t="n">
         <v>4537.457367375924</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>1.36</v>
+        <v>0.45</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>1.71</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>43075</v>
+        <v>43076</v>
       </c>
       <c r="H59" t="n">
-        <v>4502.85</v>
+        <v>4574.58</v>
       </c>
       <c r="I59" t="n">
         <v>4573.463095324371</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.03</v>
+        <v>-1.63</v>
       </c>
       <c r="L59" t="n">
-        <v>0.58</v>
+        <v>1.63</v>
       </c>
       <c r="M59" t="n">
-        <v>0.44</v>
+        <v>1.59</v>
       </c>
       <c r="N59" t="n">
-        <v>0.44</v>
+        <v>1.59</v>
       </c>
       <c r="O59" t="n">
         <v>-0.9</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>1.86</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>43081</v>
+        <v>43082</v>
       </c>
       <c r="H60" t="n">
-        <v>4589.35</v>
+        <v>4540.28</v>
       </c>
       <c r="I60" t="n">
         <v>4546.292363508534</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>0.32</v>
+        <v>-0.75</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="M60" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="N60" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="O60" t="n">
         <v>1.59</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>2.1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>43084</v>
+        <v>43087</v>
       </c>
       <c r="H61" t="n">
-        <v>4596.35</v>
+        <v>4634.67</v>
       </c>
       <c r="I61" t="n">
         <v>4619.868437002279</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.23</v>
+        <v>-2.08</v>
       </c>
       <c r="L61" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="M61" t="n">
         <v>1.44</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>2.17</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H62" t="n">
-        <v>4830.64</v>
+        <v>4712.62</v>
       </c>
       <c r="I62" t="n">
         <v>4818.503837276205</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>4.23</v>
+        <v>1.68</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="N62" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="O62" t="n">
         <v>0.83</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>2.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="H63" t="n">
-        <v>4401.06</v>
+        <v>4515.42</v>
       </c>
       <c r="I63" t="n">
         <v>4506.831803610212</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K63" t="n">
-        <v>6.61</v>
+        <v>4.18</v>
       </c>
       <c r="L63" t="n">
         <v>1.03</v>
       </c>
       <c r="M63" t="n">
-        <v>0.98</v>
+        <v>2.6</v>
       </c>
       <c r="N63" t="n">
-        <v>0.98</v>
+        <v>2.6</v>
       </c>
       <c r="O63" t="n">
         <v>-2.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>3.41</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>43147</v>
+        <v>43150</v>
       </c>
       <c r="H64" t="n">
-        <v>4491.54</v>
+        <v>4433.97</v>
       </c>
       <c r="I64" t="n">
         <v>4441.865239686206</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.53</v>
+        <v>-1.8</v>
       </c>
       <c r="L64" t="n">
-        <v>0.53</v>
+        <v>1.8</v>
       </c>
       <c r="M64" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="N64" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="O64" t="n">
         <v>2.6</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>3.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>43154</v>
+        <v>43157</v>
       </c>
       <c r="H65" t="n">
-        <v>4544.55</v>
+        <v>4597.26</v>
       </c>
       <c r="I65" t="n">
         <v>4546.174353155923</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.49</v>
+        <v>-3.68</v>
       </c>
       <c r="L65" t="n">
-        <v>2.49</v>
+        <v>3.68</v>
       </c>
       <c r="M65" t="n">
         <v>2.52</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>2.99</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>43165</v>
+        <v>43166</v>
       </c>
       <c r="H66" t="n">
-        <v>4490.84</v>
+        <v>4418.55</v>
       </c>
       <c r="I66" t="n">
         <v>4459.624873943703</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.31</v>
+        <v>-3.89</v>
       </c>
       <c r="L66" t="n">
-        <v>2.31</v>
+        <v>3.89</v>
       </c>
       <c r="M66" t="n">
-        <v>0.92</v>
+        <v>1.61</v>
       </c>
       <c r="N66" t="n">
-        <v>0.92</v>
+        <v>1.61</v>
       </c>
       <c r="O66" t="n">
         <v>1.16</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>2.71</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>43185</v>
+        <v>43186</v>
       </c>
       <c r="H67" t="n">
-        <v>4385.14</v>
+        <v>4456.83</v>
       </c>
       <c r="I67" t="n">
         <v>4426.906947744597</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>0.76</v>
+        <v>-0.87</v>
       </c>
       <c r="L67" t="n">
         <v>2.17</v>
       </c>
       <c r="M67" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="N67" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="O67" t="n">
         <v>-1.61</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>2.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>43222</v>
+        <v>43223</v>
       </c>
       <c r="H68" t="n">
-        <v>4794.77</v>
+        <v>4732.57</v>
       </c>
       <c r="I68" t="n">
         <v>4778.077353891123</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K68" t="n">
-        <v>7.58</v>
+        <v>6.19</v>
       </c>
       <c r="L68" t="n">
         <v>0.34</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>2.14</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>43244</v>
+        <v>43245</v>
       </c>
       <c r="H69" t="n">
-        <v>4360.45</v>
+        <v>4494.5</v>
       </c>
       <c r="I69" t="n">
         <v>4474.178158175239</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K69" t="n">
-        <v>7.86</v>
+        <v>5.03</v>
       </c>
       <c r="L69" t="n">
         <v>0.57</v>
       </c>
       <c r="M69" t="n">
-        <v>0.85</v>
+        <v>3.07</v>
       </c>
       <c r="N69" t="n">
-        <v>0.85</v>
+        <v>3.07</v>
       </c>
       <c r="O69" t="n">
         <v>-1.3</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>3.17</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>43252</v>
+        <v>43255</v>
       </c>
       <c r="H70" t="n">
-        <v>4439.01</v>
+        <v>4396.91</v>
       </c>
       <c r="I70" t="n">
         <v>4399.156691878056</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.23</v>
+        <v>-2.17</v>
       </c>
       <c r="L70" t="n">
-        <v>1.23</v>
+        <v>2.17</v>
       </c>
       <c r="M70" t="n">
         <v>1.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>2.79</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H71" t="n">
-        <v>4480.77</v>
+        <v>4493.01</v>
       </c>
       <c r="I71" t="n">
         <v>4484.113177031634</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.91</v>
+        <v>-2.19</v>
       </c>
       <c r="L71" t="n">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="M71" t="n">
         <v>1.37</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>2.7</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H72" t="n">
-        <v>4465.09</v>
+        <v>4387.2</v>
       </c>
       <c r="I72" t="n">
         <v>4424.769375729618</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.62</v>
+        <v>-2.35</v>
       </c>
       <c r="L72" t="n">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="M72" t="n">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="N72" t="n">
-        <v>1.49</v>
+        <v>1.74</v>
       </c>
       <c r="O72" t="n">
         <v>0.27</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>2.11</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>43283</v>
+        <v>43284</v>
       </c>
       <c r="H73" t="n">
-        <v>4358.72</v>
+        <v>4426.92</v>
       </c>
       <c r="I73" t="n">
         <v>4412.744993347582</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>0.65</v>
+        <v>-0.91</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="M73" t="n">
         <v>1.62</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>2.72</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H74" t="n">
-        <v>4408.39</v>
+        <v>4297.67</v>
       </c>
       <c r="I74" t="n">
         <v>4398.430749110498</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.42</v>
+        <v>-2.92</v>
       </c>
       <c r="L74" t="n">
-        <v>0.82</v>
+        <v>2.92</v>
       </c>
       <c r="M74" t="n">
-        <v>1.12</v>
+        <v>2.51</v>
       </c>
       <c r="N74" t="n">
-        <v>1.12</v>
+        <v>2.51</v>
       </c>
       <c r="O74" t="n">
         <v>1.56</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>3.2</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>43297</v>
+        <v>43298</v>
       </c>
       <c r="H75" t="n">
-        <v>4297.67</v>
+        <v>4437.99</v>
       </c>
       <c r="I75" t="n">
         <v>4435.277903508602</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>-3.27</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O75" t="n">
         <v>-2.51</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>3.74</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>43346</v>
+        <v>43347</v>
       </c>
       <c r="H76" t="n">
-        <v>4757.72</v>
+        <v>4619.07</v>
       </c>
       <c r="I76" t="n">
         <v>4721.528663615075</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K76" t="n">
-        <v>7.2</v>
+        <v>4.08</v>
       </c>
       <c r="L76" t="n">
         <v>2.1</v>
       </c>
       <c r="M76" t="n">
-        <v>1.44</v>
+        <v>2.91</v>
       </c>
       <c r="N76" t="n">
-        <v>1.44</v>
+        <v>2.91</v>
       </c>
       <c r="O76" t="n">
         <v>3.27</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>2.21</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>43349</v>
+        <v>43350</v>
       </c>
       <c r="H77" t="n">
-        <v>4623.72</v>
+        <v>4705.02</v>
       </c>
       <c r="I77" t="n">
         <v>4702.664521921934</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.1</v>
+        <v>-1.86</v>
       </c>
       <c r="L77" t="n">
-        <v>0.1</v>
+        <v>1.86</v>
       </c>
       <c r="M77" t="n">
-        <v>0.35</v>
+        <v>1.76</v>
       </c>
       <c r="N77" t="n">
-        <v>0.35</v>
+        <v>1.76</v>
       </c>
       <c r="O77" t="n">
         <v>-2.91</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>2.25</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H78" t="n">
-        <v>4608.6</v>
+        <v>4556.16</v>
       </c>
       <c r="I78" t="n">
         <v>4599.156537243233</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.05</v>
+        <v>-3.16</v>
       </c>
       <c r="L78" t="n">
-        <v>2.05</v>
+        <v>3.16</v>
       </c>
       <c r="M78" t="n">
         <v>2.05</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,28 +5870,28 @@
         <v>2.8</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>43355</v>
+        <v>43357</v>
       </c>
       <c r="H79" t="n">
-        <v>4587.42</v>
+        <v>4693.57</v>
       </c>
       <c r="I79" t="n">
         <v>4683.674804832981</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
       <c r="L79" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.02</v>
       </c>
       <c r="M79" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="N79" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="O79" t="n">
         <v>-1.14</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>3.06</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H80" t="n">
-        <v>4559.29</v>
+        <v>4484.43</v>
       </c>
       <c r="I80" t="n">
         <v>4549.997808085285</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.86</v>
+        <v>-4.46</v>
       </c>
       <c r="L80" t="n">
-        <v>2.86</v>
+        <v>4.46</v>
       </c>
       <c r="M80" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="N80" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="O80" t="n">
         <v>2.31</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>3.34</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>43382</v>
+        <v>43383</v>
       </c>
       <c r="H81" t="n">
-        <v>4016.33</v>
+        <v>4205.82</v>
       </c>
       <c r="I81" t="n">
         <v>4193.451185210093</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K81" t="n">
-        <v>10.44</v>
+        <v>6.21</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1.16</v>
+        <v>4.72</v>
       </c>
       <c r="N81" t="n">
-        <v>1.16</v>
+        <v>4.72</v>
       </c>
       <c r="O81" t="n">
         <v>-1.64</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,19 +6077,19 @@
         <v>5.14</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H82" t="n">
-        <v>4372.22</v>
+        <v>4296.39</v>
       </c>
       <c r="I82" t="n">
         <v>4366.577126800271</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K82" t="n">
-        <v>3.96</v>
+        <v>2.15</v>
       </c>
       <c r="L82" t="n">
         <v>3.33</v>
@@ -5124,7 +6107,19 @@
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>3</v>
+      </c>
+      <c r="U82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>2.87</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>43445</v>
+        <v>43446</v>
       </c>
       <c r="H83" t="n">
-        <v>4303.21</v>
+        <v>4411.37</v>
       </c>
       <c r="I83" t="n">
         <v>4361.291892595708</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.16</v>
+        <v>-2.68</v>
       </c>
       <c r="L83" t="n">
-        <v>0.24</v>
+        <v>2.68</v>
       </c>
       <c r="M83" t="n">
-        <v>1.54</v>
+        <v>2.51</v>
       </c>
       <c r="N83" t="n">
-        <v>1.54</v>
+        <v>2.51</v>
       </c>
       <c r="O83" t="n">
         <v>-1.73</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>3.4</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>43467</v>
+        <v>43468</v>
       </c>
       <c r="H84" t="n">
-        <v>4465.89</v>
+        <v>4415.56</v>
       </c>
       <c r="I84" t="n">
         <v>4450.706189027606</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K84" t="n">
-        <v>1.24</v>
+        <v>0.09</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,28 +6284,28 @@
         <v>2.49</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H85" t="n">
-        <v>4344.27</v>
+        <v>4390.89</v>
       </c>
       <c r="I85" t="n">
         <v>4350.678590243826</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K85" t="n">
-        <v>1.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L85" t="n">
         <v>1.87</v>
       </c>
       <c r="M85" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="N85" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="O85" t="n">
         <v>-1.13</v>
@@ -5295,7 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5322,28 +6353,28 @@
         <v>2.18</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H86" t="n">
-        <v>4328.04</v>
+        <v>4290.03</v>
       </c>
       <c r="I86" t="n">
         <v>4294.998426941026</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K86" t="n">
-        <v>-1.43</v>
+        <v>-2.3</v>
       </c>
       <c r="L86" t="n">
-        <v>1.43</v>
+        <v>2.3</v>
       </c>
       <c r="M86" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="N86" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="O86" t="n">
         <v>1.07</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>2.27</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>43518</v>
+        <v>43521</v>
       </c>
       <c r="H87" t="n">
-        <v>4178.92</v>
+        <v>4211.26</v>
       </c>
       <c r="I87" t="n">
         <v>4193.001022165808</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K87" t="n">
-        <v>2.59</v>
+        <v>1.84</v>
       </c>
       <c r="L87" t="n">
         <v>0.84</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S87" t="b">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>2.41</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H88" t="n">
-        <v>4647.38</v>
+        <v>4560.84</v>
       </c>
       <c r="I88" t="n">
         <v>4600.542611034064</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K88" t="n">
-        <v>10.36</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L88" t="n">
         <v>0.08</v>
       </c>
       <c r="M88" t="n">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="N88" t="n">
-        <v>1.09</v>
+        <v>1.86</v>
       </c>
       <c r="O88" t="n">
         <v>0.77</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S88" t="b">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>3</v>
+      </c>
+      <c r="U88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -5493,28 +6560,28 @@
         <v>2.17</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>43601</v>
+        <v>43602</v>
       </c>
       <c r="H89" t="n">
-        <v>4266.6</v>
+        <v>4342.62</v>
       </c>
       <c r="I89" t="n">
         <v>4335.669251027953</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K89" t="n">
-        <v>6.45</v>
+        <v>4.78</v>
       </c>
       <c r="L89" t="n">
         <v>0.13</v>
       </c>
       <c r="M89" t="n">
-        <v>0.48</v>
+        <v>1.78</v>
       </c>
       <c r="N89" t="n">
-        <v>0.48</v>
+        <v>1.78</v>
       </c>
       <c r="O89" t="n">
         <v>-1.86</v>
@@ -5523,7 +6590,19 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R89" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>2</v>
+      </c>
+      <c r="U89" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="90">
@@ -5550,19 +6629,19 @@
         <v>2.28</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H90" t="n">
-        <v>4569.88</v>
+        <v>4525.77</v>
       </c>
       <c r="I90" t="n">
         <v>4551.307913145043</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K90" t="n">
-        <v>5.23</v>
+        <v>4.22</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -5580,7 +6659,19 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R90" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S90" t="b">
+        <v>1</v>
+      </c>
+      <c r="T90" t="n">
+        <v>2</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -5607,22 +6698,22 @@
         <v>2.37</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H91" t="n">
-        <v>4502.13</v>
+        <v>4545.54</v>
       </c>
       <c r="I91" t="n">
         <v>4544.27158711127</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K91" t="n">
-        <v>0.52</v>
+        <v>-0.44</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="M91" t="n">
         <v>1.47</v>
@@ -5637,7 +6728,19 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5664,28 +6767,28 @@
         <v>2.34</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>43650</v>
+        <v>43651</v>
       </c>
       <c r="H92" t="n">
-        <v>4595.53</v>
+        <v>4514.24</v>
       </c>
       <c r="I92" t="n">
         <v>4516.999253370477</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>1.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M92" t="n">
-        <v>0.55</v>
+        <v>1.77</v>
       </c>
       <c r="N92" t="n">
-        <v>0.55</v>
+        <v>1.77</v>
       </c>
       <c r="O92" t="n">
         <v>0.96</v>
@@ -5694,7 +6797,19 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R92" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S92" t="b">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -5721,19 +6836,19 @@
         <v>2.19</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>43714</v>
+        <v>43717</v>
       </c>
       <c r="H93" t="n">
-        <v>3959.66</v>
+        <v>4012.24</v>
       </c>
       <c r="I93" t="n">
         <v>4001.065754666256</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K93" t="n">
-        <v>12.29</v>
+        <v>11.12</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5751,7 +6866,19 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S93" t="b">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3</v>
+      </c>
+      <c r="U93" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -5778,28 +6905,28 @@
         <v>3.28</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>43724</v>
+        <v>43725</v>
       </c>
       <c r="H94" t="n">
-        <v>4009.56</v>
+        <v>3928.6</v>
       </c>
       <c r="I94" t="n">
         <v>3933.005660585124</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.08</v>
       </c>
       <c r="L94" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="M94" t="n">
-        <v>0.92</v>
+        <v>2.02</v>
       </c>
       <c r="N94" t="n">
-        <v>0.92</v>
+        <v>2.02</v>
       </c>
       <c r="O94" t="n">
         <v>1.33</v>
@@ -5808,7 +6935,19 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5835,28 +6974,28 @@
         <v>3.22</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H95" t="n">
-        <v>3877.3</v>
+        <v>4151.49</v>
       </c>
       <c r="I95" t="n">
         <v>4002.880114090101</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
-        <v>1.31</v>
+        <v>-5.67</v>
       </c>
       <c r="L95" t="n">
-        <v>0.35</v>
+        <v>5.67</v>
       </c>
       <c r="M95" t="n">
-        <v>0.35</v>
+        <v>7.07</v>
       </c>
       <c r="N95" t="n">
-        <v>0.35</v>
+        <v>7.07</v>
       </c>
       <c r="O95" t="n">
         <v>-2.02</v>
@@ -5865,7 +7004,19 @@
         <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S95" t="b">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5892,28 +7043,28 @@
         <v>4.7</v>
       </c>
       <c r="G96" s="1" t="n">
-        <v>43738</v>
+        <v>43739</v>
       </c>
       <c r="H96" t="n">
-        <v>4094.15</v>
+        <v>4004.37</v>
       </c>
       <c r="I96" t="n">
         <v>4057.421807587019</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>-1.38</v>
+        <v>-3.54</v>
       </c>
       <c r="L96" t="n">
-        <v>1.38</v>
+        <v>3.54</v>
       </c>
       <c r="M96" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="N96" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="O96" t="n">
         <v>7.07</v>
@@ -5922,7 +7073,19 @@
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S96" t="b">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -5949,22 +7112,22 @@
         <v>5</v>
       </c>
       <c r="G97" s="1" t="n">
-        <v>43755</v>
+        <v>43756</v>
       </c>
       <c r="H97" t="n">
-        <v>4040.48</v>
+        <v>4093.99</v>
       </c>
       <c r="I97" t="n">
         <v>4076.532841326769</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.9</v>
+        <v>-2.24</v>
       </c>
       <c r="L97" t="n">
-        <v>0.9</v>
+        <v>2.24</v>
       </c>
       <c r="M97" t="n">
         <v>2.24</v>
@@ -5979,7 +7142,19 @@
         <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S97" t="b">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -6006,28 +7181,28 @@
         <v>3.44</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>43801</v>
+        <v>43802</v>
       </c>
       <c r="H98" t="n">
-        <v>4351.97</v>
+        <v>4296.09</v>
       </c>
       <c r="I98" t="n">
         <v>4302.659611187159</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K98" t="n">
-        <v>6.3</v>
+        <v>4.94</v>
       </c>
       <c r="L98" t="n">
         <v>0.42</v>
       </c>
       <c r="M98" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="N98" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="O98" t="n">
         <v>1.32</v>
@@ -6036,7 +7211,19 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S98" t="b">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>3</v>
+      </c>
+      <c r="U98" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -6063,19 +7250,19 @@
         <v>2.48</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>43811</v>
+        <v>43812</v>
       </c>
       <c r="H99" t="n">
-        <v>4244.84</v>
+        <v>4286.13</v>
       </c>
       <c r="I99" t="n">
         <v>4272.350336609779</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K99" t="n">
-        <v>1.19</v>
+        <v>0.23</v>
       </c>
       <c r="L99" t="n">
         <v>0.59</v>
@@ -6093,7 +7280,19 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S99" t="b">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6120,28 +7319,28 @@
         <v>2.72</v>
       </c>
       <c r="G100" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H100" t="n">
-        <v>4382.27</v>
+        <v>4276.76</v>
       </c>
       <c r="I100" t="n">
         <v>4341.215775034737</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K100" t="n">
-        <v>2.24</v>
+        <v>-0.22</v>
       </c>
       <c r="L100" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M100" t="n">
-        <v>1.09</v>
+        <v>2.41</v>
       </c>
       <c r="N100" t="n">
-        <v>1.09</v>
+        <v>2.41</v>
       </c>
       <c r="O100" t="n">
         <v>0.97</v>
@@ -6150,7 +7349,19 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S100" t="b">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
+        <v>2</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -6177,28 +7388,28 @@
         <v>2.74</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H101" t="n">
-        <v>4316.97</v>
+        <v>4399.53</v>
       </c>
       <c r="I101" t="n">
         <v>4393.938922221863</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.87</v>
       </c>
       <c r="L101" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.87</v>
       </c>
       <c r="M101" t="n">
-        <v>0.87</v>
+        <v>1.91</v>
       </c>
       <c r="N101" t="n">
-        <v>0.87</v>
+        <v>1.91</v>
       </c>
       <c r="O101" t="n">
         <v>-2.41</v>
@@ -6207,7 +7418,19 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R101" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S101" t="b">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6234,19 +7457,19 @@
         <v>2.73</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H102" t="n">
-        <v>4593.02</v>
+        <v>4558.07</v>
       </c>
       <c r="I102" t="n">
         <v>4568.005102969678</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K102" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -6264,7 +7487,19 @@
         <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R102" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S102" t="b">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>2</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -6291,22 +7526,22 @@
         <v>2.11</v>
       </c>
       <c r="G103" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H103" t="n">
-        <v>4547.97</v>
+        <v>4606.14</v>
       </c>
       <c r="I103" t="n">
         <v>4553.358829002692</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K103" t="n">
-        <v>0.22</v>
+        <v>-1.05</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M103" t="n">
         <v>1.53</v>
@@ -6321,7 +7556,19 @@
         <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R103" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S103" t="b">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6348,28 +7595,28 @@
         <v>3.04</v>
       </c>
       <c r="G104" s="1" t="n">
-        <v>43875</v>
+        <v>43878</v>
       </c>
       <c r="H104" t="n">
-        <v>4531.7</v>
+        <v>4463.51</v>
       </c>
       <c r="I104" t="n">
         <v>4520.994688162201</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K104" t="n">
-        <v>-1.62</v>
+        <v>-3.1</v>
       </c>
       <c r="L104" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="M104" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="N104" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O104" t="n">
         <v>1.28</v>
@@ -6378,7 +7625,19 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R104" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S104" t="b">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>1</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -6405,22 +7664,22 @@
         <v>2.5</v>
       </c>
       <c r="G105" s="1" t="n">
-        <v>43880</v>
+        <v>43881</v>
       </c>
       <c r="H105" t="n">
-        <v>4521.8</v>
+        <v>4553.96</v>
       </c>
       <c r="I105" t="n">
         <v>4551.897306311553</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K105" t="n">
-        <v>-1.31</v>
+        <v>-2.03</v>
       </c>
       <c r="L105" t="n">
-        <v>1.31</v>
+        <v>2.03</v>
       </c>
       <c r="M105" t="n">
         <v>1.7</v>
@@ -6435,7 +7694,19 @@
         <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R105" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S105" t="b">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6462,22 +7733,22 @@
         <v>2.54</v>
       </c>
       <c r="G106" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H106" t="n">
-        <v>4463.91</v>
+        <v>4417.16</v>
       </c>
       <c r="I106" t="n">
         <v>4438.144781887642</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>-1.98</v>
+        <v>-3</v>
       </c>
       <c r="L106" t="n">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="M106" t="n">
         <v>1.92</v>
@@ -6492,7 +7763,19 @@
         <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R106" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S106" t="b">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -6519,19 +7802,19 @@
         <v>2.73</v>
       </c>
       <c r="G107" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H107" t="n">
-        <v>2975.93</v>
+        <v>3100.93</v>
       </c>
       <c r="I107" t="n">
         <v>3086.85728112883</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K107" t="n">
-        <v>32.63</v>
+        <v>29.8</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -6549,7 +7832,19 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R107" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S107" t="b">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
+        <v>3</v>
+      </c>
+      <c r="U107" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -6576,28 +7871,28 @@
         <v>10.7</v>
       </c>
       <c r="G108" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H108" t="n">
-        <v>3219.55</v>
+        <v>3042.74</v>
       </c>
       <c r="I108" t="n">
         <v>3102.594102479504</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K108" t="n">
-        <v>3.83</v>
+        <v>-1.88</v>
       </c>
       <c r="L108" t="n">
         <v>2.53</v>
       </c>
       <c r="M108" t="n">
-        <v>4.91</v>
+        <v>5.49</v>
       </c>
       <c r="N108" t="n">
-        <v>4.91</v>
+        <v>5.49</v>
       </c>
       <c r="O108" t="n">
         <v>4.2</v>
@@ -6606,7 +7901,19 @@
         <v>1</v>
       </c>
       <c r="Q108" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R108" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S108" t="b">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
+        <v>2</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -6633,22 +7940,22 @@
         <v>6.33</v>
       </c>
       <c r="G109" s="1" t="n">
-        <v>43978</v>
+        <v>43979</v>
       </c>
       <c r="H109" t="n">
-        <v>3196.63</v>
+        <v>3247.07</v>
       </c>
       <c r="I109" t="n">
         <v>3234.701884642448</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K109" t="n">
-        <v>-5.06</v>
+        <v>-6.72</v>
       </c>
       <c r="L109" t="n">
-        <v>5.06</v>
+        <v>6.72</v>
       </c>
       <c r="M109" t="n">
         <v>2.41</v>
@@ -6663,7 +7970,19 @@
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R109" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S109" t="b">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6690,19 +8009,19 @@
         <v>4.68</v>
       </c>
       <c r="G110" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H110" t="n">
-        <v>3741.5</v>
+        <v>3676.95</v>
       </c>
       <c r="I110" t="n">
         <v>3680.152143330488</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K110" t="n">
-        <v>15.23</v>
+        <v>13.24</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6720,7 +8039,19 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R110" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S110" t="b">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
+        <v>2</v>
+      </c>
+      <c r="U110" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -6747,22 +8078,22 @@
         <v>3.24</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>44029</v>
+        <v>44032</v>
       </c>
       <c r="H111" t="n">
-        <v>3760.55</v>
+        <v>3797.59</v>
       </c>
       <c r="I111" t="n">
         <v>3763.508738086302</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>-2.27</v>
+        <v>-3.28</v>
       </c>
       <c r="L111" t="n">
-        <v>2.27</v>
+        <v>3.28</v>
       </c>
       <c r="M111" t="n">
         <v>2.06</v>
@@ -6777,7 +8108,19 @@
         <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R111" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S111" t="b">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6804,22 +8147,22 @@
         <v>3.3</v>
       </c>
       <c r="G112" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H112" t="n">
-        <v>3759.05</v>
+        <v>3730.23</v>
       </c>
       <c r="I112" t="n">
         <v>3734.117091962677</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K112" t="n">
-        <v>-1.01</v>
+        <v>-1.77</v>
       </c>
       <c r="L112" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="M112" t="n">
         <v>1.83</v>
@@ -6834,7 +8177,19 @@
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R112" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S112" t="b">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
+        <v>2</v>
+      </c>
+      <c r="U112" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -6861,22 +8216,22 @@
         <v>2.78</v>
       </c>
       <c r="G113" s="1" t="n">
-        <v>44048</v>
+        <v>44049</v>
       </c>
       <c r="H113" t="n">
-        <v>3819.66</v>
+        <v>3874.88</v>
       </c>
       <c r="I113" t="n">
         <v>3833.907551592236</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>-2.4</v>
+        <v>-3.88</v>
       </c>
       <c r="L113" t="n">
-        <v>2.4</v>
+        <v>3.88</v>
       </c>
       <c r="M113" t="n">
         <v>1.76</v>
@@ -6891,7 +8246,19 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R113" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S113" t="b">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>1</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6918,28 +8285,28 @@
         <v>2.96</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H114" t="n">
-        <v>4354.18</v>
+        <v>4184.42</v>
       </c>
       <c r="I114" t="n">
         <v>4251.9617662193</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K114" t="n">
-        <v>12.37</v>
+        <v>7.99</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="N114" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="O114" t="n">
         <v>1.45</v>
@@ -6948,7 +8315,19 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R114" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S114" t="b">
+        <v>1</v>
+      </c>
+      <c r="T114" t="n">
+        <v>2</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -6975,19 +8354,19 @@
         <v>3.42</v>
       </c>
       <c r="G115" s="1" t="n">
-        <v>44088</v>
+        <v>44089</v>
       </c>
       <c r="H115" t="n">
-        <v>4251.93</v>
+        <v>4281.3</v>
       </c>
       <c r="I115" t="n">
         <v>4252.167788760906</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K115" t="n">
-        <v>-1.61</v>
+        <v>-2.32</v>
       </c>
       <c r="L115" t="n">
         <v>3.31</v>
@@ -7005,7 +8384,19 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R115" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S115" t="b">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7032,28 +8423,28 @@
         <v>3.32</v>
       </c>
       <c r="G116" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H116" t="n">
-        <v>4291.97</v>
+        <v>4113.32</v>
       </c>
       <c r="I116" t="n">
         <v>4195.719958963115</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>0.25</v>
+        <v>-3.92</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="M116" t="n">
-        <v>0.7</v>
+        <v>4.16</v>
       </c>
       <c r="N116" t="n">
-        <v>0.7</v>
+        <v>4.16</v>
       </c>
       <c r="O116" t="n">
         <v>0.6899999999999999</v>
@@ -7062,7 +8453,19 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R116" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S116" t="b">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7089,22 +8492,22 @@
         <v>4</v>
       </c>
       <c r="G117" s="1" t="n">
-        <v>44099</v>
+        <v>44102</v>
       </c>
       <c r="H117" t="n">
-        <v>4091.45</v>
+        <v>4247.62</v>
       </c>
       <c r="I117" t="n">
         <v>4107.04824013187</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K117" t="n">
-        <v>0.53</v>
+        <v>-3.27</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="M117" t="n">
         <v>3.88</v>
@@ -7119,7 +8522,19 @@
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R117" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S117" t="b">
+        <v>1</v>
+      </c>
+      <c r="T117" t="n">
+        <v>2</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -7146,28 +8561,28 @@
         <v>5.29</v>
       </c>
       <c r="G118" s="1" t="n">
-        <v>44118</v>
+        <v>44119</v>
       </c>
       <c r="H118" t="n">
-        <v>4205.81</v>
+        <v>4122.43</v>
       </c>
       <c r="I118" t="n">
         <v>4157.637298123824</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>-0.98</v>
+        <v>-2.95</v>
       </c>
       <c r="L118" t="n">
-        <v>1.48</v>
+        <v>2.95</v>
       </c>
       <c r="M118" t="n">
-        <v>1.21</v>
+        <v>1.98</v>
       </c>
       <c r="N118" t="n">
-        <v>1.21</v>
+        <v>1.98</v>
       </c>
       <c r="O118" t="n">
         <v>3.82</v>
@@ -7176,7 +8591,19 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R118" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S118" t="b">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7203,22 +8630,22 @@
         <v>3.4</v>
       </c>
       <c r="G119" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H119" t="n">
-        <v>4252.89</v>
+        <v>4274.14</v>
       </c>
       <c r="I119" t="n">
         <v>4262.579874700959</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K119" t="n">
-        <v>-3.16</v>
+        <v>-3.68</v>
       </c>
       <c r="L119" t="n">
-        <v>3.16</v>
+        <v>3.68</v>
       </c>
       <c r="M119" t="n">
         <v>1.43</v>
@@ -7233,7 +8660,19 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R119" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S119" t="b">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>1</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7260,28 +8699,28 @@
         <v>2.75</v>
       </c>
       <c r="G120" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H120" t="n">
-        <v>5360.09</v>
+        <v>5079.58</v>
       </c>
       <c r="I120" t="n">
         <v>5258.837406507449</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K120" t="n">
-        <v>25.41</v>
+        <v>18.84</v>
       </c>
       <c r="L120" t="n">
         <v>1.68</v>
       </c>
       <c r="M120" t="n">
-        <v>2.41</v>
+        <v>5.23</v>
       </c>
       <c r="N120" t="n">
-        <v>2.41</v>
+        <v>5.23</v>
       </c>
       <c r="O120" t="n">
         <v>0.5</v>
@@ -7290,7 +8729,19 @@
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R120" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S120" t="b">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>3</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -7317,22 +8768,22 @@
         <v>3.72</v>
       </c>
       <c r="G121" s="1" t="n">
-        <v>44189</v>
+        <v>44193</v>
       </c>
       <c r="H121" t="n">
-        <v>5243.99</v>
+        <v>5310.31</v>
       </c>
       <c r="I121" t="n">
         <v>5268.438400728966</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K121" t="n">
-        <v>-3.24</v>
+        <v>-4.54</v>
       </c>
       <c r="L121" t="n">
-        <v>3.45</v>
+        <v>4.54</v>
       </c>
       <c r="M121" t="n">
         <v>2.75</v>
@@ -7347,7 +8798,19 @@
         <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R121" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S121" t="b">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7374,28 +8837,28 @@
         <v>3.55</v>
       </c>
       <c r="G122" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H122" t="n">
-        <v>5781.14</v>
+        <v>5654.93</v>
       </c>
       <c r="I122" t="n">
         <v>5708.975339780666</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K122" t="n">
-        <v>8.869999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="L122" t="n">
         <v>0.22</v>
       </c>
       <c r="M122" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="N122" t="n">
-        <v>1.29</v>
+        <v>2.18</v>
       </c>
       <c r="O122" t="n">
         <v>1.26</v>
@@ -7404,7 +8867,19 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R122" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S122" t="b">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>2</v>
+      </c>
+      <c r="U122" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -7431,22 +8906,22 @@
         <v>3.51</v>
       </c>
       <c r="G123" s="1" t="n">
-        <v>44215</v>
+        <v>44216</v>
       </c>
       <c r="H123" t="n">
-        <v>5817.63</v>
+        <v>5895.55</v>
       </c>
       <c r="I123" t="n">
         <v>5853.572822569906</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K123" t="n">
-        <v>-2.88</v>
+        <v>-4.26</v>
       </c>
       <c r="L123" t="n">
-        <v>2.88</v>
+        <v>4.26</v>
       </c>
       <c r="M123" t="n">
         <v>2.88</v>
@@ -7461,7 +8936,19 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R123" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S123" t="b">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7488,28 +8975,28 @@
         <v>3.87</v>
       </c>
       <c r="G124" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H124" t="n">
-        <v>5700.48</v>
+        <v>5580.72</v>
       </c>
       <c r="I124" t="n">
         <v>5667.344313718377</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K124" t="n">
-        <v>-3.31</v>
+        <v>-5.34</v>
       </c>
       <c r="L124" t="n">
-        <v>3.31</v>
+        <v>5.34</v>
       </c>
       <c r="M124" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="N124" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="O124" t="n">
         <v>1.34</v>
@@ -7518,7 +9005,19 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R124" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S124" t="b">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7545,28 +9044,28 @@
         <v>4.15</v>
       </c>
       <c r="G125" s="1" t="n">
-        <v>44225</v>
+        <v>44228</v>
       </c>
       <c r="H125" t="n">
-        <v>5520.23</v>
+        <v>5781.02</v>
       </c>
       <c r="I125" t="n">
         <v>5725.074845083192</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K125" t="n">
-        <v>1.08</v>
+        <v>-3.59</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O125" t="n">
         <v>-2.1</v>
@@ -7575,7 +9074,19 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R125" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S125" t="b">
+        <v>1</v>
+      </c>
+      <c r="T125" t="n">
+        <v>2</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -7602,19 +9113,19 @@
         <v>4.54</v>
       </c>
       <c r="G126" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H126" t="n">
-        <v>6158.14</v>
+        <v>6049.18</v>
       </c>
       <c r="I126" t="n">
         <v>6132.029600822431</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K126" t="n">
-        <v>6.52</v>
+        <v>4.64</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -7632,7 +9143,19 @@
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R126" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S126" t="b">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -7659,28 +9182,28 @@
         <v>3.88</v>
       </c>
       <c r="G127" s="1" t="n">
-        <v>44251</v>
+        <v>44252</v>
       </c>
       <c r="H127" t="n">
-        <v>6179.32</v>
+        <v>6295.96</v>
       </c>
       <c r="I127" t="n">
         <v>6283.691401000448</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>-2.15</v>
+        <v>-4.08</v>
       </c>
       <c r="L127" t="n">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="M127" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="N127" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="O127" t="n">
         <v>-1.77</v>
@@ -7689,7 +9212,19 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R127" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S127" t="b">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>1</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7716,22 +9251,22 @@
         <v>3.79</v>
       </c>
       <c r="G128" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H128" t="n">
-        <v>6231.51</v>
+        <v>6065.79</v>
       </c>
       <c r="I128" t="n">
         <v>6193.683075173646</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K128" t="n">
-        <v>-1.02</v>
+        <v>-3.66</v>
       </c>
       <c r="L128" t="n">
-        <v>2.84</v>
+        <v>3.66</v>
       </c>
       <c r="M128" t="n">
         <v>2.84</v>
@@ -7746,7 +9281,19 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R128" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S128" t="b">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7773,22 +9320,22 @@
         <v>3.72</v>
       </c>
       <c r="G129" s="1" t="n">
-        <v>44286</v>
+        <v>44287</v>
       </c>
       <c r="H129" t="n">
-        <v>6024.14</v>
+        <v>6142.74</v>
       </c>
       <c r="I129" t="n">
         <v>6097.946615334832</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K129" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.27</v>
       </c>
       <c r="L129" t="n">
-        <v>0.85</v>
+        <v>1.27</v>
       </c>
       <c r="M129" t="n">
         <v>2.27</v>
@@ -7803,7 +9350,19 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R129" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S129" t="b">
+        <v>1</v>
+      </c>
+      <c r="T129" t="n">
+        <v>2</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -7830,28 +9389,28 @@
         <v>3.85</v>
       </c>
       <c r="G130" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H130" t="n">
-        <v>6125.1</v>
+        <v>5711.57</v>
       </c>
       <c r="I130" t="n">
         <v>5937.017799136771</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>-0.29</v>
+        <v>-7.02</v>
       </c>
       <c r="L130" t="n">
-        <v>2.35</v>
+        <v>7.02</v>
       </c>
       <c r="M130" t="n">
-        <v>2.35</v>
+        <v>6.75</v>
       </c>
       <c r="N130" t="n">
-        <v>2.35</v>
+        <v>6.75</v>
       </c>
       <c r="O130" t="n">
         <v>1.97</v>
@@ -7860,7 +9419,19 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S130" t="b">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -7887,22 +9458,22 @@
         <v>5.68</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>44313</v>
+        <v>44314</v>
       </c>
       <c r="H131" t="n">
-        <v>5936.95</v>
+        <v>6040.23</v>
       </c>
       <c r="I131" t="n">
         <v>6035.776382699215</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K131" t="n">
-        <v>-3.95</v>
+        <v>-5.75</v>
       </c>
       <c r="L131" t="n">
-        <v>3.95</v>
+        <v>5.75</v>
       </c>
       <c r="M131" t="n">
         <v>2.73</v>
@@ -7917,7 +9488,19 @@
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R131" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S131" t="b">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>1</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7944,19 +9527,19 @@
         <v>4.05</v>
       </c>
       <c r="G132" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H132" t="n">
-        <v>6596.4</v>
+        <v>6514.56</v>
       </c>
       <c r="I132" t="n">
         <v>6516.180163386392</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K132" t="n">
-        <v>9.210000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="L132" t="n">
         <v>2.78</v>
@@ -7974,7 +9557,19 @@
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R132" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S132" t="b">
+        <v>1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>3</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="133">
@@ -8001,22 +9596,22 @@
         <v>2.49</v>
       </c>
       <c r="G133" s="1" t="n">
-        <v>44372</v>
+        <v>44375</v>
       </c>
       <c r="H133" t="n">
-        <v>6560.53</v>
+        <v>6589.38</v>
       </c>
       <c r="I133" t="n">
         <v>6585.171857806796</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.71</v>
+        <v>-1.15</v>
       </c>
       <c r="L133" t="n">
-        <v>0.71</v>
+        <v>1.15</v>
       </c>
       <c r="M133" t="n">
         <v>1.76</v>
@@ -8031,7 +9626,19 @@
         <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S133" t="b">
+        <v>1</v>
+      </c>
+      <c r="T133" t="n">
+        <v>2</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -8058,28 +9665,28 @@
         <v>2.29</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H134" t="n">
-        <v>6783.49</v>
+        <v>6664.26</v>
       </c>
       <c r="I134" t="n">
         <v>6724.680423422486</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K134" t="n">
-        <v>2.95</v>
+        <v>1.14</v>
       </c>
       <c r="L134" t="n">
         <v>0.85</v>
       </c>
       <c r="M134" t="n">
-        <v>0.58</v>
+        <v>1.76</v>
       </c>
       <c r="N134" t="n">
-        <v>0.58</v>
+        <v>1.76</v>
       </c>
       <c r="O134" t="n">
         <v>0.44</v>
@@ -8088,7 +9695,19 @@
         <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R134" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S134" t="b">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>1</v>
+      </c>
+      <c r="U134" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -8115,28 +9734,28 @@
         <v>1.89</v>
       </c>
       <c r="G135" s="1" t="n">
-        <v>44406</v>
+        <v>44407</v>
       </c>
       <c r="H135" t="n">
-        <v>6649.88</v>
+        <v>6752.77</v>
       </c>
       <c r="I135" t="n">
         <v>6735.040654501337</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K135" t="n">
-        <v>0.22</v>
+        <v>-1.33</v>
       </c>
       <c r="L135" t="n">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="M135" t="n">
-        <v>0.92</v>
+        <v>1.55</v>
       </c>
       <c r="N135" t="n">
-        <v>0.92</v>
+        <v>1.55</v>
       </c>
       <c r="O135" t="n">
         <v>-1.76</v>
@@ -8145,7 +9764,19 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S135" t="b">
+        <v>1</v>
+      </c>
+      <c r="T135" t="n">
+        <v>2</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -8172,22 +9803,22 @@
         <v>1.95</v>
       </c>
       <c r="G136" s="1" t="n">
-        <v>44414</v>
+        <v>44417</v>
       </c>
       <c r="H136" t="n">
-        <v>6778.59</v>
+        <v>6705.01</v>
       </c>
       <c r="I136" t="n">
         <v>6743.634368581673</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K136" t="n">
-        <v>0.38</v>
+        <v>-0.71</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="M136" t="n">
         <v>1.44</v>
@@ -8202,7 +9833,19 @@
         <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R136" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S136" t="b">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8229,28 +9872,28 @@
         <v>2.27</v>
       </c>
       <c r="G137" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H137" t="n">
-        <v>6518.14</v>
+        <v>6667.87</v>
       </c>
       <c r="I137" t="n">
         <v>6526.579068530989</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K137" t="n">
-        <v>2.79</v>
+        <v>0.55</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="N137" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O137" t="n">
         <v>-1.09</v>
@@ -8259,7 +9902,19 @@
         <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R137" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S137" t="b">
+        <v>1</v>
+      </c>
+      <c r="T137" t="n">
+        <v>2</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -8286,28 +9941,28 @@
         <v>2.81</v>
       </c>
       <c r="G138" s="1" t="n">
-        <v>44456</v>
+        <v>44459</v>
       </c>
       <c r="H138" t="n">
-        <v>7213.23</v>
+        <v>7041.88</v>
       </c>
       <c r="I138" t="n">
         <v>7105.250161392736</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K138" t="n">
-        <v>8.18</v>
+        <v>5.61</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>0.85</v>
+        <v>2.38</v>
       </c>
       <c r="N138" t="n">
-        <v>0.85</v>
+        <v>2.38</v>
       </c>
       <c r="O138" t="n">
         <v>2.3</v>
@@ -8316,7 +9971,19 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R138" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S138" t="b">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -8343,28 +10010,28 @@
         <v>2.92</v>
       </c>
       <c r="G139" s="1" t="n">
-        <v>44460</v>
+        <v>44461</v>
       </c>
       <c r="H139" t="n">
-        <v>7078.98</v>
+        <v>7289.02</v>
       </c>
       <c r="I139" t="n">
         <v>7247.838269271884</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.53</v>
+        <v>-3.51</v>
       </c>
       <c r="L139" t="n">
-        <v>0.53</v>
+        <v>3.51</v>
       </c>
       <c r="M139" t="n">
-        <v>0.53</v>
+        <v>2.97</v>
       </c>
       <c r="N139" t="n">
-        <v>0.53</v>
+        <v>2.97</v>
       </c>
       <c r="O139" t="n">
         <v>-2.38</v>
@@ -8373,7 +10040,19 @@
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R139" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S139" t="b">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8400,19 +10079,19 @@
         <v>3.29</v>
       </c>
       <c r="G140" s="1" t="n">
-        <v>44488</v>
+        <v>44489</v>
       </c>
       <c r="H140" t="n">
-        <v>7852.43</v>
+        <v>7755.16</v>
       </c>
       <c r="I140" t="n">
         <v>7818.580462418279</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K140" t="n">
-        <v>7.73</v>
+        <v>6.4</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -8430,7 +10109,19 @@
         <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R140" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S140" t="b">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
+        <v>2</v>
+      </c>
+      <c r="U140" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -8457,22 +10148,22 @@
         <v>3.71</v>
       </c>
       <c r="G141" s="1" t="n">
-        <v>44501</v>
+        <v>44502</v>
       </c>
       <c r="H141" t="n">
-        <v>7775.41</v>
+        <v>7875.53</v>
       </c>
       <c r="I141" t="n">
         <v>7862.16096404663</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K141" t="n">
-        <v>-0.26</v>
+        <v>-1.55</v>
       </c>
       <c r="L141" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.55</v>
       </c>
       <c r="M141" t="n">
         <v>2.67</v>
@@ -8487,7 +10178,19 @@
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R141" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S141" t="b">
+        <v>1</v>
+      </c>
+      <c r="T141" t="n">
+        <v>2</v>
+      </c>
+      <c r="U141" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -8514,28 +10217,28 @@
         <v>3.56</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H142" t="n">
-        <v>7949.46</v>
+        <v>7798.52</v>
       </c>
       <c r="I142" t="n">
         <v>7867.774292645881</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="L142" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="M142" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O142" t="n">
         <v>1.29</v>
@@ -8544,7 +10247,19 @@
         <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R142" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S142" t="b">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8571,19 +10286,19 @@
         <v>2.89</v>
       </c>
       <c r="G143" s="1" t="n">
-        <v>44537</v>
+        <v>44538</v>
       </c>
       <c r="H143" t="n">
-        <v>7490.53</v>
+        <v>7611.97</v>
       </c>
       <c r="I143" t="n">
         <v>7591.5888508644</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>3.95</v>
+        <v>2.39</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -8601,7 +10316,19 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R143" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S143" t="b">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
+        <v>2</v>
+      </c>
+      <c r="U143" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -8628,28 +10355,28 @@
         <v>3.58</v>
       </c>
       <c r="G144" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H144" t="n">
-        <v>7516.99</v>
+        <v>7284.57</v>
       </c>
       <c r="I144" t="n">
         <v>7446.950266472595</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K144" t="n">
-        <v>-1.25</v>
+        <v>-4.3</v>
       </c>
       <c r="L144" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="M144" t="n">
-        <v>0.9</v>
+        <v>3.09</v>
       </c>
       <c r="N144" t="n">
-        <v>0.9</v>
+        <v>3.09</v>
       </c>
       <c r="O144" t="n">
         <v>1.62</v>
@@ -8658,7 +10385,19 @@
         <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R144" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S144" t="b">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -8685,22 +10424,22 @@
         <v>3.49</v>
       </c>
       <c r="G145" s="1" t="n">
-        <v>44560</v>
+        <v>44561</v>
       </c>
       <c r="H145" t="n">
-        <v>7262.48</v>
+        <v>7357.96</v>
       </c>
       <c r="I145" t="n">
         <v>7325.213648855537</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K145" t="n">
-        <v>0.3</v>
+        <v>-1.01</v>
       </c>
       <c r="L145" t="n">
-        <v>0.26</v>
+        <v>1.01</v>
       </c>
       <c r="M145" t="n">
         <v>1.55</v>
@@ -8715,7 +10454,19 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R145" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S145" t="b">
+        <v>1</v>
+      </c>
+      <c r="T145" t="n">
+        <v>2</v>
+      </c>
+      <c r="U145" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -8742,28 +10493,28 @@
         <v>3.07</v>
       </c>
       <c r="G146" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H146" t="n">
-        <v>7747.65</v>
+        <v>7549.75</v>
       </c>
       <c r="I146" t="n">
         <v>7724.948900239596</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K146" t="n">
-        <v>5.3</v>
+        <v>2.61</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>0.29</v>
+        <v>0.54</v>
       </c>
       <c r="N146" t="n">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="O146" t="n">
         <v>1.31</v>
@@ -8772,7 +10523,19 @@
         <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R146" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S146" t="b">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -8799,22 +10562,22 @@
         <v>5.01</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H147" t="n">
-        <v>7599.95</v>
+        <v>7691.5</v>
       </c>
       <c r="I147" t="n">
         <v>7687.059587507769</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K147" t="n">
-        <v>-0.66</v>
+        <v>-1.88</v>
       </c>
       <c r="L147" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="M147" t="n">
         <v>1.24</v>
@@ -8829,7 +10592,19 @@
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R147" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S147" t="b">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
+        <v>2</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -8856,28 +10631,28 @@
         <v>6.18</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H148" t="n">
-        <v>7362.15</v>
+        <v>7047</v>
       </c>
       <c r="I148" t="n">
         <v>7216.202281172537</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K148" t="n">
-        <v>-4.28</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L148" t="n">
-        <v>5.02</v>
+        <v>8.67</v>
       </c>
       <c r="M148" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="N148" t="n">
-        <v>2.18</v>
+        <v>4.28</v>
       </c>
       <c r="O148" t="n">
         <v>1.2</v>
@@ -8886,7 +10661,19 @@
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R148" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S148" t="b">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -8913,19 +10700,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H149" t="n">
-        <v>7092.2</v>
+        <v>7217.1</v>
       </c>
       <c r="I149" t="n">
         <v>7141.047300070823</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K149" t="n">
-        <v>-0.64</v>
+        <v>-2.41</v>
       </c>
       <c r="L149" t="n">
         <v>4.86</v>
@@ -8943,7 +10730,19 @@
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R149" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S149" t="b">
+        <v>1</v>
+      </c>
+      <c r="T149" t="n">
+        <v>2</v>
+      </c>
+      <c r="U149" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -8970,19 +10769,19 @@
         <v>7.36</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H150" t="n">
-        <v>7376</v>
+        <v>7301.7</v>
       </c>
       <c r="I150" t="n">
         <v>7319.46027385244</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K150" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="L150" t="n">
         <v>2.66</v>
@@ -9000,7 +10799,19 @@
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R150" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S150" t="b">
+        <v>1</v>
+      </c>
+      <c r="T150" t="n">
+        <v>2</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -9027,19 +10838,19 @@
         <v>6.35</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H151" t="n">
-        <v>6605.1</v>
+        <v>6613.7</v>
       </c>
       <c r="I151" t="n">
         <v>6610.307210186807</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K151" t="n">
-        <v>9.539999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="L151" t="n">
         <v>2.43</v>
@@ -9057,7 +10868,19 @@
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R151" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S151" t="b">
+        <v>1</v>
+      </c>
+      <c r="T151" t="n">
+        <v>4</v>
+      </c>
+      <c r="U151" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="152">
@@ -9084,19 +10907,19 @@
         <v>5.25</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H152" t="n">
-        <v>7648.15</v>
+        <v>7405.7</v>
       </c>
       <c r="I152" t="n">
         <v>7413.885074015819</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K152" t="n">
-        <v>15.64</v>
+        <v>11.98</v>
       </c>
       <c r="L152" t="n">
         <v>0.84</v>
@@ -9105,7 +10928,7 @@
         <v>2.84</v>
       </c>
       <c r="N152" t="n">
-        <v>2.04</v>
+        <v>3.17</v>
       </c>
       <c r="O152" t="n">
         <v>0.13</v>
@@ -9114,7 +10937,19 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R152" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S152" t="b">
+        <v>1</v>
+      </c>
+      <c r="T152" t="n">
+        <v>3</v>
+      </c>
+      <c r="U152" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="153">
@@ -9141,19 +10976,19 @@
         <v>6.01</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H153" t="n">
-        <v>7445.95</v>
+        <v>7515.8</v>
       </c>
       <c r="I153" t="n">
         <v>7505.620328569613</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K153" t="n">
-        <v>-0.54</v>
+        <v>-1.49</v>
       </c>
       <c r="L153" t="n">
         <v>3.4</v>
@@ -9171,7 +11006,19 @@
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R153" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S153" t="b">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
+        <v>3</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -9198,22 +11045,22 @@
         <v>4.38</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H154" t="n">
-        <v>7234.75</v>
+        <v>7184.05</v>
       </c>
       <c r="I154" t="n">
         <v>7186.495821478611</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K154" t="n">
-        <v>-3.74</v>
+        <v>-4.41</v>
       </c>
       <c r="L154" t="n">
-        <v>4.13</v>
+        <v>5.01</v>
       </c>
       <c r="M154" t="n">
         <v>0.19</v>
@@ -9228,7 +11075,19 @@
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R154" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S154" t="b">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -9255,22 +11114,22 @@
         <v>4.37</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>44896</v>
+        <v>44897</v>
       </c>
       <c r="H155" t="n">
-        <v>7448.35</v>
+        <v>7491.1</v>
       </c>
       <c r="I155" t="n">
         <v>7449.652270286526</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K155" t="n">
-        <v>-3.68</v>
+        <v>-4.27</v>
       </c>
       <c r="L155" t="n">
-        <v>3.94</v>
+        <v>4.34</v>
       </c>
       <c r="M155" t="n">
         <v>0.46</v>
@@ -9285,7 +11144,19 @@
         <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R155" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S155" t="b">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
+        <v>2</v>
+      </c>
+      <c r="U155" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -9312,22 +11183,22 @@
         <v>3.6</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H156" t="n">
-        <v>7325.3</v>
+        <v>7214.9</v>
       </c>
       <c r="I156" t="n">
         <v>7238.527013867346</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K156" t="n">
-        <v>-2.21</v>
+        <v>-3.69</v>
       </c>
       <c r="L156" t="n">
-        <v>3.18</v>
+        <v>4.05</v>
       </c>
       <c r="M156" t="n">
         <v>0.66</v>
@@ -9342,7 +11213,19 @@
         <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R156" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S156" t="b">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9369,19 +11252,19 @@
         <v>5.11</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H157" t="n">
-        <v>6885.8</v>
+        <v>6936.4</v>
       </c>
       <c r="I157" t="n">
         <v>6894.450049751933</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K157" t="n">
-        <v>4.56</v>
+        <v>3.86</v>
       </c>
       <c r="L157" t="n">
         <v>2.31</v>
@@ -9399,7 +11282,19 @@
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R157" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S157" t="b">
+        <v>1</v>
+      </c>
+      <c r="T157" t="n">
+        <v>5</v>
+      </c>
+      <c r="U157" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -9426,19 +11321,19 @@
         <v>3.61</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>45218</v>
+        <v>45219</v>
       </c>
       <c r="H158" t="n">
-        <v>9065.5</v>
+        <v>8944.549999999999</v>
       </c>
       <c r="I158" t="n">
         <v>8956.95403950589</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K158" t="n">
-        <v>30.69</v>
+        <v>28.95</v>
       </c>
       <c r="L158" t="n">
         <v>0.63</v>
@@ -9456,7 +11351,19 @@
         <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R158" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S158" t="b">
+        <v>1</v>
+      </c>
+      <c r="T158" t="n">
+        <v>7</v>
+      </c>
+      <c r="U158" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="159">
@@ -9483,22 +11390,22 @@
         <v>4.04</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H159" t="n">
-        <v>8984.6</v>
+        <v>9074.65</v>
       </c>
       <c r="I159" t="n">
         <v>9035.596756660705</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K159" t="n">
-        <v>-0.45</v>
+        <v>-1.45</v>
       </c>
       <c r="L159" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="M159" t="n">
         <v>0.76</v>
@@ -9513,7 +11420,19 @@
         <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R159" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S159" t="b">
+        <v>1</v>
+      </c>
+      <c r="T159" t="n">
+        <v>2</v>
+      </c>
+      <c r="U159" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -9540,19 +11459,19 @@
         <v>3.68</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H160" t="n">
-        <v>10715.35</v>
+        <v>10378.5</v>
       </c>
       <c r="I160" t="n">
         <v>10575.56098330385</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K160" t="n">
-        <v>18.08</v>
+        <v>14.37</v>
       </c>
       <c r="L160" t="n">
         <v>0.54</v>
@@ -9561,7 +11480,7 @@
         <v>0.9</v>
       </c>
       <c r="N160" t="n">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="O160" t="n">
         <v>1</v>
@@ -9570,7 +11489,19 @@
         <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R160" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S160" t="b">
+        <v>1</v>
+      </c>
+      <c r="T160" t="n">
+        <v>5</v>
+      </c>
+      <c r="U160" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -9597,22 +11528,22 @@
         <v>7.06</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H161" t="n">
-        <v>10689.45</v>
+        <v>10777.2</v>
       </c>
       <c r="I161" t="n">
         <v>10736.19318332599</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>-3</v>
+        <v>-3.84</v>
       </c>
       <c r="L161" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="M161" t="n">
         <v>1.01</v>
@@ -9627,7 +11558,19 @@
         <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R161" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S161" t="b">
+        <v>1</v>
+      </c>
+      <c r="T161" t="n">
+        <v>2</v>
+      </c>
+      <c r="U161" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -9654,28 +11597,28 @@
         <v>5.07</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H162" t="n">
-        <v>11723.55</v>
+        <v>10841</v>
       </c>
       <c r="I162" t="n">
         <v>11156.87763520926</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K162" t="n">
-        <v>8.779999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="L162" t="n">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="M162" t="n">
         <v>1.18</v>
       </c>
       <c r="N162" t="n">
-        <v>1.82</v>
+        <v>7.53</v>
       </c>
       <c r="O162" t="n">
         <v>0.82</v>
@@ -9684,7 +11627,19 @@
         <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R162" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S162" t="b">
+        <v>1</v>
+      </c>
+      <c r="T162" t="n">
+        <v>3</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="163">
@@ -9711,22 +11666,22 @@
         <v>10.35</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>45456</v>
+        <v>45457</v>
       </c>
       <c r="H163" t="n">
-        <v>11947.45</v>
+        <v>12053.2</v>
       </c>
       <c r="I163" t="n">
         <v>11963.51598268528</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K163" t="n">
-        <v>-10.21</v>
+        <v>-11.18</v>
       </c>
       <c r="L163" t="n">
-        <v>10.66</v>
+        <v>11.29</v>
       </c>
       <c r="M163" t="n">
         <v>1.2</v>
@@ -9741,7 +11696,19 @@
         <v>1</v>
       </c>
       <c r="Q163" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R163" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S163" t="b">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -9768,28 +11735,28 @@
         <v>6.48</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H164" t="n">
-        <v>12625.05</v>
+        <v>12294.35</v>
       </c>
       <c r="I164" t="n">
         <v>12326.78120913376</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K164" t="n">
-        <v>4.74</v>
+        <v>2</v>
       </c>
       <c r="L164" t="n">
         <v>0.97</v>
       </c>
       <c r="M164" t="n">
-        <v>1.03</v>
+        <v>2.49</v>
       </c>
       <c r="N164" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="O164" t="n">
         <v>0.89</v>
@@ -9798,7 +11765,19 @@
         <v>0</v>
       </c>
       <c r="Q164" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R164" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S164" t="b">
+        <v>1</v>
+      </c>
+      <c r="T164" t="n">
+        <v>3</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -9825,22 +11804,22 @@
         <v>5.63</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>45525</v>
+        <v>45526</v>
       </c>
       <c r="H165" t="n">
-        <v>12938.15</v>
+        <v>13067.1</v>
       </c>
       <c r="I165" t="n">
         <v>12986.71917354149</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>-5.24</v>
+        <v>-6.29</v>
       </c>
       <c r="L165" t="n">
-        <v>5.32</v>
+        <v>6.55</v>
       </c>
       <c r="M165" t="n">
         <v>1.85</v>
@@ -9855,7 +11834,19 @@
         <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R165" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S165" t="b">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1</v>
+      </c>
+      <c r="U165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -9882,22 +11873,22 @@
         <v>4.57</v>
       </c>
       <c r="G166" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H166" t="n">
-        <v>12976.25</v>
+        <v>12812.85</v>
       </c>
       <c r="I166" t="n">
         <v>12891.45679598473</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K166" t="n">
-        <v>-0.7</v>
+        <v>-1.95</v>
       </c>
       <c r="L166" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="M166" t="n">
         <v>1.34</v>
@@ -9912,7 +11903,19 @@
         <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R166" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S166" t="b">
+        <v>1</v>
+      </c>
+      <c r="T166" t="n">
+        <v>3</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -9939,19 +11942,19 @@
         <v>5.22</v>
       </c>
       <c r="G167" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H167" t="n">
-        <v>12619.5</v>
+        <v>12726.3</v>
       </c>
       <c r="I167" t="n">
         <v>12679.96242824687</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K167" t="n">
-        <v>1.51</v>
+        <v>0.68</v>
       </c>
       <c r="L167" t="n">
         <v>3.07</v>
@@ -9969,7 +11972,19 @@
         <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R167" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S167" t="b">
+        <v>1</v>
+      </c>
+      <c r="T167" t="n">
+        <v>3</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -9996,19 +12011,19 @@
         <v>4.68</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H168" t="n">
-        <v>13027.2</v>
+        <v>12683.15</v>
       </c>
       <c r="I168" t="n">
         <v>12757.05317973938</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K168" t="n">
-        <v>2.36</v>
+        <v>-0.34</v>
       </c>
       <c r="L168" t="n">
         <v>1.12</v>
@@ -10017,7 +12032,7 @@
         <v>1.61</v>
       </c>
       <c r="N168" t="n">
-        <v>0.88</v>
+        <v>2.64</v>
       </c>
       <c r="O168" t="n">
         <v>0.85</v>
@@ -10026,7 +12041,19 @@
         <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R168" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S168" t="b">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -10053,19 +12080,19 @@
         <v>5.7</v>
       </c>
       <c r="G169" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H169" t="n">
-        <v>11507</v>
+        <v>11699.5</v>
       </c>
       <c r="I169" t="n">
         <v>11522.43448348574</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K169" t="n">
-        <v>9.27</v>
+        <v>7.76</v>
       </c>
       <c r="L169" t="n">
         <v>3.52</v>
@@ -10083,7 +12110,19 @@
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R169" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S169" t="b">
+        <v>1</v>
+      </c>
+      <c r="T169" t="n">
+        <v>4</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -10110,28 +12149,28 @@
         <v>6.28</v>
       </c>
       <c r="G170" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H170" t="n">
-        <v>11181.8</v>
+        <v>10769.5</v>
       </c>
       <c r="I170" t="n">
         <v>10964.5477177176</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K170" t="n">
-        <v>-4.42</v>
+        <v>-7.95</v>
       </c>
       <c r="L170" t="n">
-        <v>4.86</v>
+        <v>11.26</v>
       </c>
       <c r="M170" t="n">
-        <v>0.85</v>
+        <v>7.15</v>
       </c>
       <c r="N170" t="n">
-        <v>2.89</v>
+        <v>3.69</v>
       </c>
       <c r="O170" t="n">
         <v>1.67</v>
@@ -10140,7 +12179,19 @@
         <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R170" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S170" t="b">
+        <v>1</v>
+      </c>
+      <c r="T170" t="n">
+        <v>2</v>
+      </c>
+      <c r="U170" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -10167,28 +12218,28 @@
         <v>6.79</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H171" t="n">
-        <v>11226.3</v>
+        <v>11540.8</v>
       </c>
       <c r="I171" t="n">
         <v>11500.35181524974</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K171" t="n">
-        <v>-4.24</v>
+        <v>-7.16</v>
       </c>
       <c r="L171" t="n">
-        <v>4.74</v>
+        <v>7.39</v>
       </c>
       <c r="M171" t="n">
         <v>2.48</v>
       </c>
       <c r="N171" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="O171" t="n">
         <v>-3.69</v>
@@ -10197,7 +12248,19 @@
         <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R171" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S171" t="b">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10224,19 +12287,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H172" t="n">
-        <v>12943.35</v>
+        <v>12727.7</v>
       </c>
       <c r="I172" t="n">
         <v>12821.77353272366</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K172" t="n">
-        <v>12.15</v>
+        <v>10.28</v>
       </c>
       <c r="L172" t="n">
         <v>1.51</v>
@@ -10254,7 +12317,19 @@
         <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R172" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S172" t="b">
+        <v>1</v>
+      </c>
+      <c r="T172" t="n">
+        <v>3</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -10281,19 +12356,19 @@
         <v>5.51</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="H173" t="n">
-        <v>13340.55</v>
+        <v>13433.85</v>
       </c>
       <c r="I173" t="n">
         <v>13429.52776498373</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K173" t="n">
-        <v>-4.82</v>
+        <v>-5.55</v>
       </c>
       <c r="L173" t="n">
         <v>5.82</v>
@@ -10311,7 +12386,19 @@
         <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R173" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S173" t="b">
+        <v>1</v>
+      </c>
+      <c r="T173" t="n">
+        <v>2</v>
+      </c>
+      <c r="U173" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -10338,25 +12425,25 @@
         <v>4.27</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H174" t="n">
-        <v>13107.65</v>
+        <v>12925.9</v>
       </c>
       <c r="I174" t="n">
         <v>13001.59195384833</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K174" t="n">
-        <v>-2.43</v>
+        <v>-3.78</v>
       </c>
       <c r="L174" t="n">
-        <v>3.27</v>
+        <v>4.05</v>
       </c>
       <c r="M174" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="N174" t="n">
         <v>1.39</v>
@@ -10368,7 +12455,19 @@
         <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R174" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S174" t="b">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -10395,22 +12494,22 @@
         <v>4.46</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="H175" t="n">
-        <v>13037.6</v>
+        <v>13083.05</v>
       </c>
       <c r="I175" t="n">
         <v>13065.45725447843</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K175" t="n">
-        <v>-0.86</v>
+        <v>-1.22</v>
       </c>
       <c r="L175" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M175" t="n">
         <v>1.38</v>
@@ -10425,7 +12524,19 @@
         <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R175" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S175" t="b">
+        <v>1</v>
+      </c>
+      <c r="T175" t="n">
+        <v>3</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="176">
@@ -10452,22 +12563,22 @@
         <v>3.5</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H176" t="n">
-        <v>12905.35</v>
+        <v>12822.3</v>
       </c>
       <c r="I176" t="n">
         <v>12861.57184926429</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K176" t="n">
-        <v>-1.36</v>
+        <v>-1.99</v>
       </c>
       <c r="L176" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="M176" t="n">
         <v>0.46</v>
@@ -10482,7 +12593,19 @@
         <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R176" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S176" t="b">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -10509,22 +12632,22 @@
         <v>3.72</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H177" t="n">
-        <v>13034.55</v>
+        <v>13149.55</v>
       </c>
       <c r="I177" t="n">
         <v>13042.19873499712</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K177" t="n">
-        <v>-1.66</v>
+        <v>-2.55</v>
       </c>
       <c r="L177" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="M177" t="n">
         <v>0.39</v>
@@ -10539,7 +12662,19 @@
         <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R177" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S177" t="b">
+        <v>1</v>
+      </c>
+      <c r="T177" t="n">
+        <v>2</v>
+      </c>
+      <c r="U177" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -10566,19 +12701,19 @@
         <v>3.57</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H178" t="n">
-        <v>13741.35</v>
+        <v>13534.35</v>
       </c>
       <c r="I178" t="n">
         <v>13655.72628361967</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K178" t="n">
-        <v>4.5</v>
+        <v>2.93</v>
       </c>
       <c r="L178" t="n">
         <v>1.02</v>
@@ -10596,7 +12731,19 @@
         <v>0</v>
       </c>
       <c r="Q178" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R178" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S178" t="b">
+        <v>1</v>
+      </c>
+      <c r="T178" t="n">
+        <v>3</v>
+      </c>
+      <c r="U178" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="179">
@@ -10623,19 +12770,19 @@
         <v>5.16</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H179" t="n">
-        <v>13644.9</v>
+        <v>13868.65</v>
       </c>
       <c r="I179" t="n">
         <v>13761.40995746953</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.82</v>
+        <v>-2.47</v>
       </c>
       <c r="L179" t="n">
         <v>4.03</v>
@@ -10653,7 +12800,19 @@
         <v>0</v>
       </c>
       <c r="Q179" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R179" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S179" t="b">
+        <v>1</v>
+      </c>
+      <c r="T179" t="n">
+        <v>3</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="180">
@@ -10680,22 +12839,22 @@
         <v>6.58</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H180" t="n">
-        <v>13289.85</v>
+        <v>13034.35</v>
       </c>
       <c r="I180" t="n">
         <v>13202.826220981</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K180" t="n">
-        <v>-4.17</v>
+        <v>-6.02</v>
       </c>
       <c r="L180" t="n">
-        <v>5.99</v>
+        <v>6.78</v>
       </c>
       <c r="M180" t="n">
         <v>3.35</v>
@@ -10710,7 +12869,19 @@
         <v>0</v>
       </c>
       <c r="Q180" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R180" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S180" t="b">
+        <v>1</v>
+      </c>
+      <c r="T180" t="n">
+        <v>2</v>
+      </c>
+      <c r="U180" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -10737,22 +12908,22 @@
         <v>5.32</v>
       </c>
       <c r="G181" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H181" t="n">
-        <v>13207.3</v>
+        <v>13406.35</v>
       </c>
       <c r="I181" t="n">
         <v>13251.56039259047</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K181" t="n">
-        <v>-1.33</v>
+        <v>-2.85</v>
       </c>
       <c r="L181" t="n">
-        <v>2.23</v>
+        <v>2.96</v>
       </c>
       <c r="M181" t="n">
         <v>3.52</v>
@@ -10767,7 +12938,19 @@
         <v>0</v>
       </c>
       <c r="Q181" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R181" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S181" t="b">
+        <v>1</v>
+      </c>
+      <c r="T181" t="n">
+        <v>2</v>
+      </c>
+      <c r="U181" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -10794,19 +12977,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G182" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H182" t="n">
-        <v>14107.5</v>
+        <v>13994.75</v>
       </c>
       <c r="I182" t="n">
         <v>14089.64176883116</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K182" t="n">
-        <v>5.23</v>
+        <v>4.39</v>
       </c>
       <c r="L182" t="n">
         <v>2.68</v>
@@ -10824,7 +13007,19 @@
         <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R182" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S182" t="b">
+        <v>1</v>
+      </c>
+      <c r="T182" t="n">
+        <v>3</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="183">
@@ -10851,19 +13046,19 @@
         <v>4.97</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H183" t="n">
-        <v>14575.8</v>
+        <v>14595.65</v>
       </c>
       <c r="I183" t="n">
         <v>14578.90195184775</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K183" t="n">
-        <v>-4.15</v>
+        <v>-4.29</v>
       </c>
       <c r="L183" t="n">
         <v>4.52</v>
@@ -10881,7 +13076,19 @@
         <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R183" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S183" t="b">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -10908,19 +13115,19 @@
         <v>4.36</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H184" t="n">
-        <v>14672.55</v>
+        <v>14604.4</v>
       </c>
       <c r="I184" t="n">
         <v>14650.35324268048</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K184" t="n">
-        <v>0.53</v>
+        <v>0.06</v>
       </c>
       <c r="L184" t="n">
         <v>2.49</v>
@@ -10938,7 +13145,19 @@
         <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R184" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S184" t="b">
+        <v>1</v>
+      </c>
+      <c r="T184" t="n">
+        <v>4</v>
+      </c>
+      <c r="U184" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -10989,6 +13208,14 @@
       <c r="Q185" t="n">
         <v>33</v>
       </c>
+      <c r="R185" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S185" t="b">
+        <v>1</v>
+      </c>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15947,7 +18174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6">
@@ -15957,7 +18184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -15967,7 +18194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -15977,7 +18204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -15987,7 +18214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -15997,7 +18224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="11">
@@ -16007,7 +18234,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -16017,7 +18244,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -16027,7 +18254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.2</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="14">
@@ -16037,7 +18264,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15">
@@ -16047,7 +18274,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.36</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="16">
@@ -16057,7 +18284,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="17">
@@ -16067,7 +18294,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.63</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="18">
@@ -16077,7 +18304,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="19">
@@ -16087,7 +18314,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.46</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="20">
@@ -16097,7 +18324,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.06</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="21">
@@ -16107,7 +18334,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.66</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="22">
@@ -16117,7 +18344,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -16127,7 +18354,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -16137,7 +18364,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.56</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="25">
@@ -16147,7 +18374,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.27</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="26">
@@ -16157,7 +18384,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="27">
@@ -16167,7 +18394,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.67</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="28">
@@ -16177,7 +18404,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
